--- a/daily_matches/job_matches_2026-08-20.xlsx
+++ b/daily_matches/job_matches_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G59"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ETL Developer</t>
+          <t>Systems Engineer SME</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>VTG Defense</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tysons Corner, VA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>27.8</v>
+        <v>28.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Glue, Redshift, BigQuery, Synapse, Data Lake, Kinesis, Apache Airflow, CI/CD, Jenkins</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, BigQuery, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=706e3b72b66ba001</t>
+          <t>https://www.indeed.com/viewjob?jk=73e738969e8679aa</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ETL Developer</t>
+          <t>Senior Production Operations Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>27.8</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Glue, Redshift, BigQuery, Synapse, Data Lake, Kinesis, Apache Airflow, CI/CD, Jenkins</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Snowflake, MySQL, Python</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,67 +531,67 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a6fc35c45c62e0e</t>
+          <t>https://www.indeed.com/viewjob?jk=84465101ecfed6f0</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Data Scientist, Commercial Analytics</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Capio Group</t>
+          <t>ExxonMobil</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Spring, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>25.6</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, Cortex, TensorFlow, PyTorch, AWS SageMaker, GCP Vertex AI, Azure ML, Redshift</t>
+          <t>Data Scientist, LangChain, RAG, Copilot, TensorFlow, PyTorch, Azure ML, MLflow, CI/CD, Databricks</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c700a6e916d3d0c4</t>
+          <t>https://www.indeed.com/viewjob?jk=2cdeb00b4ff281b3</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Homes.com - Arlington, VA</t>
+          <t>Machine Learning Engineer Graduate (E-Commerce Supply Chain &amp; Logistics - LLM/Agent) - 2027 Start (PhD)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>24.4</v>
+        <v>13.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Copilot, Prompt Engineering, S3, BigQuery, Data Lake, CI/CD, Terraform, Git</t>
+          <t>AI Engineer, Machine Learning Engineer, LangChain, RAG, LLaMA, Hugging Face, TensorFlow, PyTorch, Python, R</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8764f80e093a42ae</t>
+          <t>https://www.indeed.com/viewjob?jk=600a1d65828ca95f</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Database Administrator (0597U) Berkeley IT, #88217</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>University of California Berkeley</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Berkeley, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>24.4</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, LLaMA, Gemini, Copilot, S3, Docker, Kubernetes, CI/CD, Jenkins</t>
+          <t>RAG, CI/CD, Terraform, PostgreSQL, MySQL, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d0497d85a50331b</t>
+          <t>https://www.indeed.com/viewjob?jk=a83c7618f2ffb5df</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Java Backend Software Engineer II - Databricks / PySpark / AWS</t>
+          <t>Sr SDET Engineer (Selenium, Playwright / Cypress, Java / Python, FTE, Onsite)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>20</v>
+        <v>13.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, Copilot, S3, EC2, Docker, Kubernetes, CI/CD, Git</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af14f051f56d396e</t>
+          <t>https://www.indeed.com/viewjob?jk=0297dc62d73e5356</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Howmet Aerospace</t>
+          <t>Teichert Construction</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>20</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Mistral, Hugging Face, Prompt Engineering, TensorFlow, PyTorch</t>
+          <t>AI Engineer, Data Scientist, Generative AI, Git, Databricks, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,277 +706,277 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=533361150ecd3311</t>
+          <t>https://www.indeed.com/viewjob?jk=3bc7127badc11937</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AI Architect (GenAI &amp; Agentic AI)</t>
+          <t>Co-Op, DevOps Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>StatusNeo Technology Consulting</t>
+          <t>LiveRamp</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>20</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Gemini, Pinecone, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD</t>
+          <t>Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, MySQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d27648e192521308</t>
+          <t>https://www.indeed.com/viewjob?jk=40696df5eb2aec78</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer – AWS</t>
+          <t>Cybersecurity Sr Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>CBRE</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>18.9</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Glue, Redshift, Kinesis, Kubernetes, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RAG, S3, EC2, Kubernetes, Jenkins, GitHub Actions, Terraform, Git, MySQL, Python</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=616635db842b8721</t>
+          <t>https://www.indeed.com/viewjob?jk=ad4d8655d28b7570</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Applied AI Engineer</t>
+          <t>Sr. Software Engineer - Applied AI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>18.9</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Hugging Face, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=700eee01521f136e</t>
+          <t>https://www.indeed.com/viewjob?jk=a7e04582db2fd9d3</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Sr. Software Engineer - Applied AI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Entrata</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>17.8</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, LLaMA, Hugging Face, AWS SageMaker, Docker, Kubernetes, Terraform, Git</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Hugging Face, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8e0ed081c7f9b12</t>
+          <t>https://www.indeed.com/viewjob?jk=66183a6a907073d9</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Production Operations Engineer</t>
+          <t>Sr. Software Engineer - Applied AI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16.7</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Snowflake, MySQL, Python</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Hugging Face, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8937a2d408f44ee</t>
+          <t>https://www.indeed.com/viewjob?jk=eecbe2aa8baf2134</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Engineer in Residence (AI Full-Stack)</t>
+          <t>Senior Engineer - Applied AI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>AI Fund</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Pinecone, Prompt Engineering, Git, PostgreSQL, MongoDB, NoSQL, Python</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Hugging Face, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d105d2d7c4308aa3</t>
+          <t>https://www.indeed.com/viewjob?jk=c6dd5779eded592b</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - AI Infrastructure Integration, High Performance Compute</t>
+          <t>Sr. Software Engineer - Applied AI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Generative AI, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, spaCy, Gensim, CI/CD, Tableau, Python</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Hugging Face, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60a65bcc460b5aa7</t>
+          <t>https://www.indeed.com/viewjob?jk=4ff22db21a487f52</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Hadoop</t>
+          <t>Quality Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>CloudBees Inc</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, S3, Kubernetes, CI/CD, Databricks, Kafka, Hadoop, NoSQL, Python, SQL</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,67 +986,67 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0ac15a01e20fc4f</t>
+          <t>https://www.indeed.com/viewjob?jk=fa64a37e56abf48c</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sr Engineer, FW &amp; Product Test</t>
+          <t>Forward-deployed AI Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>SCAN Health Plan</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Longmont, CO, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Copilot, Prompt Engineering, TensorFlow, PyTorch, CI/CD, Git, Python</t>
+          <t>AI Engineer, LangChain, RAG, Prompt Engineering, FastAPI, Git, Snowflake, Databricks, Python, R</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26ec03f5de0470ea</t>
+          <t>https://www.indeed.com/viewjob?jk=f92ea4f4f33fd68c</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Machine Learning</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange</t>
+          <t>Globant</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, TensorFlow, PyTorch, CI/CD, Git, Databricks, Tableau, Power BI, Python</t>
+          <t>Machine Learning Engineer, Generative AI, LangChain, RAG, Copilot, Prompt Engineering, CI/CD, Jenkins, Git, Python</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d60ca1406acf737</t>
+          <t>https://www.indeed.com/viewjob?jk=23bec263d7f0038e</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>QA Automation Engineer</t>
+          <t>Senior Software QA Test Development Engineer - Diagnostics</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, PostgreSQL, MongoDB, Python, SQL</t>
+          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ce4b3e97856dbbe</t>
+          <t>https://www.indeed.com/viewjob?jk=6b2e1f973cd779d8</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AI Engineer / Job Requisition 1023714309</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Alameda Alliance for Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Alameda, CA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, Docker, Kubernetes, Python, SQL</t>
+          <t>RAG, Copilot, S3, CI/CD, Git, Snowflake, Tableau, Python, SQL, R</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,67 +1126,67 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4f902eaf03a65b4</t>
+          <t>https://www.indeed.com/viewjob?jk=dbb5062224932805</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>NLP AI Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>UKG</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lowell, MA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, LangChain, RAG, LLaMA, PyTorch, Docker, Kubernetes, Python, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f13e6764cba1f7f5</t>
+          <t>https://www.indeed.com/viewjob?jk=1a2ffae4b9711c6f</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Python Software Architect</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Teichert Construction</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, S3, Glue, CI/CD, PostgreSQL, Python, SQL</t>
+          <t>Data Scientist, RAG, XGBoost, LightGBM, Git, Databricks, Tableau, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6aecd8ca526fdf3</t>
+          <t>https://www.indeed.com/viewjob?jk=82085acc9832952a</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>OCI Solutions Architect</t>
+          <t>Site Reliability Engineer III</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>LexisNexis Risk Solutions</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, MySQL, Python, SQL</t>
+          <t>RAG, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15965a432c4c0c4b</t>
+          <t>https://www.indeed.com/viewjob?jk=40c525e9ac046705</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Cloud-Native Architect</t>
+          <t>Site Reliability Engineer III</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Kafka, Python, R, Java</t>
+          <t>RAG, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb6470494901645e</t>
+          <t>https://www.indeed.com/viewjob?jk=361321672b77d8b9</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Conversational AI Engineer</t>
+          <t>DATA SCIENTIST</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Dollar General</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Goodlettsville, TN, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Gemini, Mistral, Prompt Engineering, Kubernetes, CI/CD, Python</t>
+          <t>Data Scientist, Git, Databricks, PySpark, Tableau, Matplotlib, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26fa5e098f3bb86f</t>
+          <t>https://www.indeed.com/viewjob?jk=b9e9e55514658931</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Autonomous Learning Engineer</t>
+          <t>Machine Learning Engineer Graduate (E-Commerce Supply Chain &amp; Logistics) - 2027 Start</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Python, R</t>
+          <t>AI Engineer, Machine Learning Engineer, RAG, TensorFlow, PyTorch, Python, R, Java, Optimization</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe60ba55dcfb9a34</t>
+          <t>https://www.indeed.com/viewjob?jk=cacd3a0af5341411</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Engineer, Database Administration</t>
+          <t>Machine Learning Engineer Graduate (E-Commerce Supply Chain &amp; Logistics) - 2027 Start</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Guardian Life</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Bethlehem, PA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RAG, EC2, Kubernetes, CI/CD, Jenkins, Terraform, Git, SQL, R, Scala</t>
+          <t>AI Engineer, Machine Learning Engineer, RAG, TensorFlow, PyTorch, Python, R, Java, Optimization</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4af900edf5ab1204</t>
+          <t>https://www.indeed.com/viewjob?jk=897ed8c758cf78cb</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Full Stack</t>
+          <t>Senior Software Engineer, Data</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CoBank</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Greenwood Village, CO, US USA</t>
+          <t>Manasquan, NJ, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, TensorFlow, Docker, Kubernetes, CI/CD, Git, Python, SQL, R</t>
+          <t>RAG, BigQuery, Data Lake, Snowflake, Databricks, BigQuery, Python, SQL, R</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=022bb95c5104146a</t>
+          <t>https://www.indeed.com/viewjob?jk=8092575b540f4d54</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer, Full Stack</t>
+          <t>Machine Learning Engineer, Generative ML, Level 4</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CoBank</t>
+          <t>Snap Inc.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Greenwood Village, CO, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, TensorFlow, Docker, Kubernetes, CI/CD, Git, Python, SQL, R</t>
+          <t>Machine Learning Engineer, Generative AI, RAG, TensorFlow, PyTorch, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7049d0189a722c2b</t>
+          <t>https://www.indeed.com/viewjob?jk=6cee28a7bb683517</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior AI-Native Software Engineer</t>
+          <t>Machine Learning Engineer, Generative ML, Level 5</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Lean Solutions Group</t>
+          <t>Snap Inc.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Python, SQL, R, Java</t>
+          <t>Machine Learning Engineer, Generative AI, RAG, TensorFlow, PyTorch, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d5a3eebe7959425</t>
+          <t>https://www.indeed.com/viewjob?jk=5cbb3372737db3a5</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Java Application Architect</t>
+          <t>Data Engineer 1, Insights Delivery Finance (Hybrid - Seattle, WA)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, MySQL, SQL, R</t>
+          <t>BigQuery, CI/CD, Git, BigQuery, Tableau, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,987 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=786034c3bb092539</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Full Stack Solutions Developer – Java</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, MySQL, SQL, R</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d4141f79f39713f5</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Full Stack Solutions Developer – Java</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, MySQL, SQL, R</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f78ec24375fa841a</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Software Developer - Telecom Bill Calculations Software (Back End, Python)</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>National Information Solutions Cooperative (NISC)</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>St. Louis, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, S3, EC2, Docker, Kubernetes, CI/CD, Git, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f91d5232f542a491</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Cloud Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Q2ebanking</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Terraform, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=04718bbf73627185</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>AMH</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Las Vegas, NV, US USA</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>CI/CD, Databricks, Kafka, NoSQL, Tableau, Power BI, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=092148f8cd728c31</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Moderna</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Cambridge, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, PyTorch, Docker, Git, Python, R, Optimization, Bayesian, Hypothesis Testing</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bed2b236fa5ae2ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Cybersecurity Lab Engineer</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Merlin International</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>RAG, Cortex, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=09c6c2f52e251262</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer – Generative AI- Adobe Experience Platform</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Adobe</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Snowflake, MySQL, NoSQL, Python, SQL, R, Java, Optimization</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=184aa5e458372d3b</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Test Automation Engineer</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ff3e40b5b3a8b19e</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Senior .NET Solutions Developer</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=82a483eb701ec1f7</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Python Solutions Engineer</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>RAG, TensorFlow, PyTorch, S3, Glue, CI/CD, PostgreSQL, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7870cd3f671322e2</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Integration Platform Developer</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, Kafka, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c2be0511e13ca8c2</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Java Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>RAG, S3, Docker, Kubernetes, CI/CD, Kafka, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fdb7a41af779bc2e</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Software Engineer III (US)</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>TD</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Mount Laurel, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, Jenkins, Git, MySQL, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=016231f42801289f</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Software Engineer II - Identity</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Electronic Arts</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Redwood City, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Jenkins, Git, NoSQL, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=788fdf7747961e1f</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Infrastructure Engineer, Database</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>LangChain</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>10</v>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>LangChain, RAG, S3, Kubernetes, CI/CD, Terraform, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=302a2623c657924c</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Sr. Engineer, Cloud HPC Platform</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Ayar Labs</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>10</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>RAG, S3, EC2, Terraform, Git, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6894092cdbcfe061</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>DevSecOps / Cloud Engineer</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>10</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>RAG, S3, GitHub Actions, Terraform, Git, PostgreSQL, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bff1a015b16f649a</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Software Engineer II – Radiation Effects Tooling</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Blue Origin</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>10</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Generative AI, LangChain, RAG, TensorFlow, PyTorch, Git, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=98c8e0cce6a9d000</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>OpenShift Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>10</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=46a76c030486bcd6</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Mule ESB Developer</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>10</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, Kafka, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5d4212a58288ad36</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Software Engineer – AI Systems</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Mutual of Omaha Mortgage</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Irvine, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>10</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>RAG, Prompt Engineering, Docker, CI/CD, Git, MySQL, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dca7ee3e6b7d322c</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>FanDuel</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>10</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Docker, Kubernetes, Terraform, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c308d3e3a113391d</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>FanDuel</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>10</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Docker, Kubernetes, Terraform, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=660ff547eb660f95</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer / Data Scientist – Python &amp; GenAI</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Recutify Inc.</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Tampa, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>10</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>Data Scientist, TensorFlow, PySpark, Hadoop, MySQL, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=81784d139822ef09</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Sr. Data Analyst/Sales Enablement</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Associated Materials</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Cuyahoga Falls, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>10</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>RAG, Databricks, PySpark, Power BI, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b2702be181dcb3d5</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Data Scientist Senior</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Technology Ventures</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>10</v>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>Data Scientist, TensorFlow, PyTorch, OpenCV, Data Lake, Snowflake, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e43d4fb9ee5c26f5</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Sr. Data Scientist - Credit Risk</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Purpose Financial</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Greenville, SC, US USA</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>10</v>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>Data Scientist, XGBoost, LightGBM, Git, Tableau, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=75382bb4b07644b1</t>
+          <t>https://www.indeed.com/viewjob?jk=304b246d7ce7389e</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-20.xlsx
+++ b/daily_matches/job_matches_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,130 +468,130 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Developer</t>
+          <t>Software Engineering - Senior Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>FICO</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.8</v>
+        <v>18.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, AWS SageMaker, Azure ML, Docker, Kubernetes, CI/CD, Terraform, Git</t>
+          <t>RAG, S3, Athena, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cb452da16920d81</t>
+          <t>https://www.indeed.com/viewjob?jk=2f8abb748a167939</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Kafka, PostgreSQL, Cassandra</t>
+          <t>Generative AI, RAG, Gemini, CI/CD, Git, Kafka, PostgreSQL, MongoDB, NoSQL, Python</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06c149b0229a30a1</t>
+          <t>https://www.indeed.com/viewjob?jk=b878c9ad00168635</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer Graduate (E-Commerce Supply Chain &amp; Logistics - LLM/Agent) - 2027 Start (PhD)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Machine Learning Engineer, LangChain, RAG, LLaMA, Hugging Face, TensorFlow, PyTorch, Python, R</t>
+          <t>Generative AI, RAG, Gemini, CI/CD, Git, Kafka, PostgreSQL, MongoDB, NoSQL, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27197e05cd371ba2</t>
+          <t>https://www.indeed.com/viewjob?jk=51ab8998579dcc3a</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer II - AWS/PySpark/ETL</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Quantum Sky</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, CI/CD, Git, Snowflake, Databricks, PySpark, Python, SQL, R</t>
+          <t>Gemini, Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, Terraform, Git, Kafka, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e56fac37798dfc2</t>
+          <t>https://www.indeed.com/viewjob?jk=16e7cc43379f9f1b</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BD</t>
+          <t>NetApp</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Milpitas, CA, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Java</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, FastAPI, Docker, Kubernetes, CI/CD, NoSQL, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,112 +636,497 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a923e057dc9cf63</t>
+          <t>https://www.indeed.com/viewjob?jk=fae543d1f6c9e0d2</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Engineer-II, Firmware Test Engg</t>
+          <t>Full Stack Developer - Java/ React</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Longmont, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Copilot, TensorFlow, PyTorch, CI/CD, Git, Python, R, Optimization</t>
+          <t>Generative AI, RAG, Gemini, CI/CD, Git, Kafka, MongoDB, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d35f53129aa78bb</t>
+          <t>https://www.indeed.com/viewjob?jk=f5a41ffcb11e1749</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Full Stack Developer - Java/ React</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Everfox</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
+          <t>Generative AI, RAG, Gemini, CI/CD, Git, Kafka, MongoDB, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0265a8f6cb82c099</t>
+          <t>https://www.indeed.com/viewjob?jk=60aa25871e93c329</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer III - Java/AWS</t>
+          <t>Full Stack Developer - Java/ React</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, CI/CD, Git, Kafka, MongoDB, NoSQL, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c43bab62e6ea0712</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Full Stack Developer - Java/ React</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, CI/CD, Git, Kafka, MongoDB, NoSQL, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c2fa28942f5a9923</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>AI Architect - Telecom Network Engineer</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Gemini, Copilot, Git, Snowflake, Databricks, R</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a97cd46a0a09e0e1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>AI Architect - Telecom Network Engineer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Gemini, Copilot, Git, Snowflake, Databricks, R</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1a9d60680c6d7127</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Software Engineer III - Full Stack</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>JPMorganChase</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Wilmington, DE, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>RAG, S3, Docker, Kubernetes, CI/CD, Terraform, PostgreSQL, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=633e4ef91698f188</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Senior DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Prodapt Solutions</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Richardson, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>RAG, Kinesis, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1b234d21055ac65b</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>DevOps / Site Reliability Engineer (SRE)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>NextAmp LLC</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Kubernetes, Apache Airflow, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e480055c770b0f79</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>AI Engineer II</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>EchoStar</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Herndon, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, FastAPI, Docker, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d9ddd107b0bc4108</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>AI Engineer II</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>EchoStar</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Herndon, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, FastAPI, Docker, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=833aff4a26643f10</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Senior Python/GenAI Engineer</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
         <v>10</v>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>RAG, S3, EC2, Docker, Kubernetes, CI/CD, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=63cc8d2ab08c9153</t>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Gemini, FastAPI, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=96f756b926ee8d7f</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Senior Python/GenAI Engineer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>10</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Gemini, FastAPI, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dee478fe7c2c5dc9</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Software Engineer, Global Banking &amp; Markets, Commodity Trading &amp; Sales Technology</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Goldman Sachs</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>10</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RAG, Git, MongoDB, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=71d422a378fcf05d</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-20.xlsx
+++ b/daily_matches/job_matches_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Engineering - Senior Engineer</t>
+          <t>Senior Platform Engineer – Snowflake (Azure / Entra ID)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>FICO</t>
+          <t>Integra Connect</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>15.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, S3, Athena, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, MySQL</t>
+          <t>RAG, Copilot, Cortex, AKS, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Python</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f8abb748a167939</t>
+          <t>https://www.indeed.com/viewjob?jk=7029dd2c0aa17f4f</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior DevOps Engineer (With SRE Trajectory)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Big Bridge Holdings, Inc.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, CI/CD, Git, Kafka, PostgreSQL, MongoDB, NoSQL, Python</t>
+          <t>S3, EC2, Docker, CI/CD, Jenkins, GitHub Actions, Terraform, Git, MongoDB, Python</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b878c9ad00168635</t>
+          <t>https://www.indeed.com/viewjob?jk=7e17a536e9381936</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr Data Analyst</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, CI/CD, Git, Kafka, PostgreSQL, MongoDB, NoSQL, Python</t>
+          <t>RAG, Gemini, Cortex, Snowflake, Databricks, Tableau, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,67 +566,67 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51ab8998579dcc3a</t>
+          <t>https://www.indeed.com/viewjob?jk=053ccac6300bb1a2</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Software Engineer I</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Quantum Sky</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Gemini, Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, Terraform, Git, Kafka, Python</t>
+          <t>Data Scientist, Generative AI, RAG, Docker, Jenkins, Git, NoSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16e7cc43379f9f1b</t>
+          <t>https://www.indeed.com/viewjob?jk=7fc5503a862e74b5</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Solution Architect (P4643)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NetApp</t>
+          <t>84.51°</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, FastAPI, Docker, Kubernetes, CI/CD, NoSQL, Python</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, Cortex, Data Lake, CI/CD, Snowflake, Databricks, R, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fae543d1f6c9e0d2</t>
+          <t>https://www.indeed.com/viewjob?jk=197c1260170c59d6</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Full Stack Developer - Java/ React</t>
+          <t>Solution Architect (P4643)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>84.51°</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, CI/CD, Git, Kafka, MongoDB, NoSQL, Python, SQL</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, Cortex, Data Lake, CI/CD, Snowflake, Databricks, R, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5a41ffcb11e1749</t>
+          <t>https://www.indeed.com/viewjob?jk=446cca91d73f3859</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Full Stack Developer - Java/ React</t>
+          <t>Solution Architect (P4643)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>84.51°</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, CI/CD, Git, Kafka, MongoDB, NoSQL, Python, SQL</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, Cortex, Data Lake, CI/CD, Snowflake, Databricks, R, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60aa25871e93c329</t>
+          <t>https://www.indeed.com/viewjob?jk=40c26a376d819abe</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Full Stack Developer - Java/ React</t>
+          <t>Senior Data Scientist I</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Elsevier</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, CI/CD, Git, Kafka, MongoDB, NoSQL, Python, SQL</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Python, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c43bab62e6ea0712</t>
+          <t>https://www.indeed.com/viewjob?jk=b5bffa8852f3b2f7</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Full Stack Developer - Java/ React</t>
+          <t>Senior DevOps Build Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>SAI360</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, CI/CD, Git, Kafka, MongoDB, NoSQL, Python, SQL</t>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, R, Java, Optimization</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2fa28942f5a9923</t>
+          <t>https://www.indeed.com/viewjob?jk=cd8cead2d413bb95</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI Architect - Telecom Network Engineer</t>
+          <t>Senior GCP Cloud Platform Engineer - Landing Zone / Terraform</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>DATA PULSE TECH AI LLC</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, Gemini, Copilot, Git, Snowflake, Databricks, R</t>
+          <t>Gemini, BigQuery, CI/CD, Jenkins, GitHub Actions, Terraform, Git, BigQuery, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,322 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a97cd46a0a09e0e1</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>AI Architect - Telecom Network Engineer</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, Gemini, Copilot, Git, Snowflake, Databricks, R</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1a9d60680c6d7127</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Software Engineer III - Full Stack</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>RAG, S3, Docker, Kubernetes, CI/CD, Terraform, PostgreSQL, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=633e4ef91698f188</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Senior DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Prodapt Solutions</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Richardson, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>RAG, Kinesis, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1b234d21055ac65b</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>DevOps / Site Reliability Engineer (SRE)</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>NextAmp LLC</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Kubernetes, Apache Airflow, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e480055c770b0f79</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>AI Engineer II</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>EchoStar</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Herndon, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, FastAPI, Docker, CI/CD, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d9ddd107b0bc4108</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>AI Engineer II</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>EchoStar</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Herndon, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, FastAPI, Docker, CI/CD, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=833aff4a26643f10</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Senior Python/GenAI Engineer</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>10</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Gemini, FastAPI, Git, Python, R</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=96f756b926ee8d7f</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Senior Python/GenAI Engineer</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>10</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Gemini, FastAPI, Git, Python, R</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dee478fe7c2c5dc9</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Software Engineer, Global Banking &amp; Markets, Commodity Trading &amp; Sales Technology</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Goldman Sachs</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>10</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>RAG, Git, MongoDB, NoSQL, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=71d422a378fcf05d</t>
+          <t>https://www.indeed.com/viewjob?jk=d9dad8cf3e146c2d</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-20.xlsx
+++ b/daily_matches/job_matches_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer – Snowflake (Azure / Entra ID)</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Integra Connect</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15.6</v>
+        <v>21.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Cortex, AKS, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Python</t>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Snowflake</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7029dd2c0aa17f4f</t>
+          <t>https://www.indeed.com/viewjob?jk=a9ea33155120cc34</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (With SRE Trajectory)</t>
+          <t>Generative AI Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Big Bridge Holdings, Inc.</t>
+          <t>Vforce Infotech</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>S3, EC2, Docker, CI/CD, Jenkins, GitHub Actions, Terraform, Git, MongoDB, Python</t>
+          <t>AI Engineer, Generative AI, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,67 +531,67 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e17a536e9381936</t>
+          <t>https://www.indeed.com/viewjob?jk=798cf4619231e531</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr Data Analyst</t>
+          <t>Software Engineering Intern</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Ericsson</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Cortex, Snowflake, Databricks, Tableau, Python, SQL, R, Scala</t>
+          <t>RAG, TensorFlow, PyTorch, NoSQL, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=053ccac6300bb1a2</t>
+          <t>https://www.indeed.com/viewjob?jk=20ea5317e8d6b57c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer I</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Storage Rentals of America</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>West Palm Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Docker, Jenkins, Git, NoSQL, SQL, R, Java</t>
+          <t>Generative AI, RAG, Copilot, Prompt Engineering, Data Lake, Power BI, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fc5503a862e74b5</t>
+          <t>https://www.indeed.com/viewjob?jk=1f0d0f4936165b59</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Solution Architect (P4643)</t>
+          <t>AI Automation &amp; Claude Integration Specialist</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>84.51°</t>
+          <t>Re/Max - America's Top Realty</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Cantonment, FL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, Cortex, Data Lake, CI/CD, Snowflake, Databricks, R, Scala</t>
+          <t>Generative AI, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=197c1260170c59d6</t>
+          <t>https://www.indeed.com/viewjob?jk=ab05094795d92e22</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Solution Architect (P4643)</t>
+          <t>Site Reliability Engineer III</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>84.51°</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, Cortex, Data Lake, CI/CD, Snowflake, Databricks, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, Jenkins, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=446cca91d73f3859</t>
+          <t>https://www.indeed.com/viewjob?jk=1c9b71dc127e3e48</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Solution Architect (P4643)</t>
+          <t>Machine Learning Engineer Intern (Payment Data Intelligence) - 2027 Summer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>84.51°</t>
+          <t>TikTok USDS JV</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, Cortex, Data Lake, CI/CD, Snowflake, Databricks, R, Scala</t>
+          <t>Machine Learning Engineer, RAG, Prompt Engineering, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40c26a376d819abe</t>
+          <t>https://www.indeed.com/viewjob?jk=748a08d9f5f5982c</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Scientist I</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Elsevier</t>
+          <t>Diverge Health</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Python, R</t>
+          <t>RAG, Copilot, Git, Snowflake, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5bffa8852f3b2f7</t>
+          <t>https://www.indeed.com/viewjob?jk=6d465630ca383c6e</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior DevOps Build Engineer</t>
+          <t>Senior Machine Learning Infrastructure Engineer, Recommendations and Search</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SAI360</t>
+          <t>TikTok USDS JV</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, R, Java, Optimization</t>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Python, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,42 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd8cead2d413bb95</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Senior GCP Cloud Platform Engineer - Landing Zone / Terraform</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>DATA PULSE TECH AI LLC</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>10</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Gemini, BigQuery, CI/CD, Jenkins, GitHub Actions, Terraform, Git, BigQuery, R</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d9dad8cf3e146c2d</t>
+          <t>https://www.indeed.com/viewjob?jk=b4baf68850585029</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-20.xlsx
+++ b/daily_matches/job_matches_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.1</v>
+        <v>23.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Snowflake</t>
+          <t>RAG, S3, Glue, Redshift, BigQuery, Synapse, Kinesis, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9ea33155120cc34</t>
+          <t>https://www.indeed.com/viewjob?jk=5d356376aee9aed9</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generative AI Engineer</t>
+          <t>Software Engineer II - Backend</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Vforce Infotech</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Databricks, Kafka, Python, SQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,67 +531,67 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=798cf4619231e531</t>
+          <t>https://www.indeed.com/viewjob?jk=5500d6b30d337bf5</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineering Intern</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ericsson</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, NoSQL, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>Data Scientist, Generative AI, RAG, S3, Glue, Redshift, Data Lake, Apache Airflow, Databricks, Redshift</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20ea5317e8d6b57c</t>
+          <t>https://www.indeed.com/viewjob?jk=ba4ddae196475dfd</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Storage Rentals of America</t>
+          <t>US Mobile</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>West Palm Beach, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Prompt Engineering, Data Lake, Power BI, SQL, R, Scala, Optimization</t>
+          <t>RAG, S3, Redshift, BigQuery, Snowflake, BigQuery, Redshift, Tableau, Python, SQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f0d0f4936165b59</t>
+          <t>https://www.indeed.com/viewjob?jk=38cfb69843b2db92</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI Automation &amp; Claude Integration Specialist</t>
+          <t>Machine Learning Engineer Intern (E-Commerce Supply Chain &amp; Logistics-LLM / Agent) - 2027 Start (PhD)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Re/Max - America's Top Realty</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Cantonment, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>AI Engineer, Machine Learning Engineer, LangChain, RAG, LLaMA, Hugging Face, TensorFlow, PyTorch, Python, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab05094795d92e22</t>
+          <t>https://www.indeed.com/viewjob?jk=df115f045aeb97ad</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer III</t>
+          <t>Machine Learning Engineer Intern (E-Commerce Supply Chain &amp; Logistics-LLM/Agent) - 2027 Start (PhD)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Jenkins, Terraform, Git, Python, R, Scala</t>
+          <t>AI Engineer, Machine Learning Engineer, LangChain, RAG, LLaMA, Hugging Face, TensorFlow, PyTorch, Python, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c9b71dc127e3e48</t>
+          <t>https://www.indeed.com/viewjob?jk=c6ecc7b987f75fd0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer Intern (Payment Data Intelligence) - 2027 Summer</t>
+          <t>Senior DevOps Engineer (Contract to hire)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>TikTok USDS JV</t>
+          <t>Initech Global</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, Prompt Engineering, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>S3, EC2, Kubernetes, CI/CD, Jenkins, Terraform, Git, Kafka, Python, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=748a08d9f5f5982c</t>
+          <t>https://www.indeed.com/viewjob?jk=ff58f5c88964acc3</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Diverge Health</t>
+          <t>6sense</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Git, Snowflake, Python, SQL, R, Scala, Optimization</t>
+          <t>Machine Learning Engineer, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, Databricks, Python, R, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,42 +741,322 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d465630ca383c6e</t>
+          <t>https://www.indeed.com/viewjob?jk=4c5bed4c33be7ef6</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>2027 Data &amp; AI Program - Summer Internship - Analyst - United States</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Copilot, Prompt Engineering, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c4f2f44e26d3457d</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Quality Engineering</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>CoStar Group</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>10</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Jenkins, GitHub Actions, Git, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=13aebbe6301e3200</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Application Development Senior Advisor- Hybrid</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>The Cigna Group</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Bloomfield, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>10</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>RAG, Jenkins, Git, Kafka, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4000419aead97d7c</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Azure Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>10</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=18e1aaa9c145a04c</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>UI/UX Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>FIS</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>10</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>RAG, S3, Docker, Kubernetes, CI/CD, Jenkins, Git, R, Scala</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5d71df633b508f38</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Sr. Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Oteemo, Inc</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>College Park, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>10</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Generative AI, Docker, Kubernetes, AKS, CI/CD, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=12c525deacac3e0a</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>AI DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Zscaler</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>10</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, Data Lake, Kubernetes, CI/CD, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1c139869116af60d</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>Senior Machine Learning Infrastructure Engineer, Recommendations and Search</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>TikTok USDS JV</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
         <v>10</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Python, R, Java, Scala, Optimization</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b4baf68850585029</t>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4bde01d1e803fc76</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Storage Rentals of America</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>West Palm Beach, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>10</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Git, Power BI, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6b9fb34fea0c03c0</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-20.xlsx
+++ b/daily_matches/job_matches_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer Job</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Armstrong World Industries</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Lancaster, PA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>23.3</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Redshift, BigQuery, Synapse, Kinesis, CI/CD, Terraform, Git</t>
+          <t>Data Scientist, RAG, Prompt Engineering, Glue, Data Lake, CI/CD, Git, Snowflake, Databricks, Python</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d356376aee9aed9</t>
+          <t>https://www.indeed.com/viewjob?jk=83106bef0df0d936</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer II - Backend</t>
+          <t>Senior AI/ML Full Stack Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Databricks, Kafka, Python, SQL</t>
+          <t>Generative AI, RAG, Prompt Engineering, BigQuery, Docker, CI/CD, Terraform, Git, Snowflake, BigQuery</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5500d6b30d337bf5</t>
+          <t>https://www.indeed.com/viewjob?jk=eb01dfa6121864df</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>C.H. Robinson</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, S3, Glue, Redshift, Data Lake, Apache Airflow, Databricks, Redshift</t>
+          <t>Data Scientist, LangChain, RAG, Copilot, Kubernetes, CI/CD, Git, Snowflake, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba4ddae196475dfd</t>
+          <t>https://www.indeed.com/viewjob?jk=0cea1d8921bab123</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>GPU MLOps Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>US Mobile</t>
+          <t>Molex</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Lisle, IL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, S3, Redshift, BigQuery, Snowflake, BigQuery, Redshift, Tableau, Python, SQL</t>
+          <t>Data Scientist, Azure ML, MLflow, Docker, Kubernetes, AKS, CI/CD, Terraform, Power BI, R</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38cfb69843b2db92</t>
+          <t>https://www.indeed.com/viewjob?jk=9d3ebe703eaedf55</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer Intern (E-Commerce Supply Chain &amp; Logistics-LLM / Agent) - 2027 Start (PhD)</t>
+          <t>GPU MLOps Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Molex</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, Machine Learning Engineer, LangChain, RAG, LLaMA, Hugging Face, TensorFlow, PyTorch, Python, R</t>
+          <t>Data Scientist, Azure ML, MLflow, Docker, Kubernetes, AKS, CI/CD, Terraform, Power BI, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df115f045aeb97ad</t>
+          <t>https://www.indeed.com/viewjob?jk=0bb4337faf7af1cf</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer Intern (E-Commerce Supply Chain &amp; Logistics-LLM/Agent) - 2027 Start (PhD)</t>
+          <t>GPU MLOps Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Molex</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, Machine Learning Engineer, LangChain, RAG, LLaMA, Hugging Face, TensorFlow, PyTorch, Python, R</t>
+          <t>Data Scientist, Azure ML, MLflow, Docker, Kubernetes, AKS, CI/CD, Terraform, Power BI, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6ecc7b987f75fd0</t>
+          <t>https://www.indeed.com/viewjob?jk=27bc057c56cea960</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (Contract to hire)</t>
+          <t>Snowflake_DBT Developers</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Initech Global</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>S3, EC2, Kubernetes, CI/CD, Jenkins, Terraform, Git, Kafka, Python, R</t>
+          <t>S3, Glue, Data Lake, CI/CD, Terraform, Snowflake, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff58f5c88964acc3</t>
+          <t>https://www.indeed.com/viewjob?jk=acb81b67805de775</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr. Machine Learning Engineer</t>
+          <t>Intern - Data Full Stack Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>6sense</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, Databricks, Python, R, Scala</t>
+          <t>Generative AI, RAG, Data Lake, CI/CD, Snowflake, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c5bed4c33be7ef6</t>
+          <t>https://www.indeed.com/viewjob?jk=861b5b837191e360</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2027 Data &amp; AI Program - Summer Internship - Analyst - United States</t>
+          <t>Senior Data Engineer, Berxi</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Berkshire Hathaway Specialty Insurance</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, Prompt Engineering, Snowflake, Databricks, Python, SQL, R, Scala</t>
+          <t>RAG, CI/CD, GitHub Actions, Git, Databricks, NoSQL, Power BI, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4f2f44e26d3457d</t>
+          <t>https://www.indeed.com/viewjob?jk=bdcd811be7d4a19d</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Quality Engineering</t>
+          <t>Senior Software Engineer, Asynchronous Processing</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Klaviyo</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Jenkins, GitHub Actions, Git, SQL, R, Java</t>
+          <t>RAG, FastAPI, Kubernetes, Terraform, Git, Kafka, Python, R, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13aebbe6301e3200</t>
+          <t>https://www.indeed.com/viewjob?jk=8bed4367aac850f3</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Application Development Senior Advisor- Hybrid</t>
+          <t>Data Analyst III/Sr</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>EQT Corporation</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bloomfield, CT, US USA</t>
+          <t>Canonsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Jenkins, Git, Kafka, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Data Lake, Git, Databricks, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,217 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4000419aead97d7c</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Azure Cloud Engineer</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>10</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=18e1aaa9c145a04c</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>UI/UX Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>FIS</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>10</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>RAG, S3, Docker, Kubernetes, CI/CD, Jenkins, Git, R, Scala</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5d71df633b508f38</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Sr. Cloud Engineer</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Oteemo, Inc</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>College Park, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>10</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Generative AI, Docker, Kubernetes, AKS, CI/CD, Terraform, Git, Python, R</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=12c525deacac3e0a</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>AI DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Zscaler</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>10</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>RAG, Gemini, Data Lake, Kubernetes, CI/CD, Terraform, Git, Python, R</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1c139869116af60d</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Senior Machine Learning Infrastructure Engineer, Recommendations and Search</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>TikTok USDS JV</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>10</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Python, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4bde01d1e803fc76</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Storage Rentals of America</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>West Palm Beach, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>10</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, Git, Power BI, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6b9fb34fea0c03c0</t>
+          <t>https://www.indeed.com/viewjob?jk=cdf2419224aa656d</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-20.xlsx
+++ b/daily_matches/job_matches_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer Job</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Armstrong World Industries</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Lancaster, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>18.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Prompt Engineering, Glue, Data Lake, CI/CD, Git, Snowflake, Databricks, Python</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, MLflow, CI/CD, Jenkins, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83106bef0df0d936</t>
+          <t>https://www.indeed.com/viewjob?jk=dc92f44a3afb58a3</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior AI/ML Full Stack Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>CURE Auto Insurance</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, BigQuery, Docker, CI/CD, Terraform, Git, Snowflake, BigQuery</t>
+          <t>RAG, Redshift, BigQuery, Data Lake, Kinesis, CI/CD, Snowflake, Databricks, BigQuery, Redshift</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb01dfa6121864df</t>
+          <t>https://www.indeed.com/viewjob?jk=23d8077cddaec91f</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Senior Data Engineer — AI/ML Data Platforms</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>C.H. Robinson</t>
+          <t>T. Mims Corp.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lakeland, FL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>17.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, Copilot, Kubernetes, CI/CD, Git, Snowflake, MongoDB, NoSQL</t>
+          <t>AI Engineer, RAG, Pinecone, S3, Glue, Athena, Docker, Kubernetes, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cea1d8921bab123</t>
+          <t>https://www.indeed.com/viewjob?jk=ac713d0689b63faa</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GPU MLOps Engineer</t>
+          <t>Data Scientist - AI/ML Solutions PPCO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Molex</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Lisle, IL, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.2</v>
+        <v>17.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, Azure ML, MLflow, Docker, Kubernetes, AKS, CI/CD, Terraform, Power BI, R</t>
+          <t>Data Scientist, Generative AI, RAG, MLflow, FastAPI, CI/CD, Git, Databricks, PySpark, Tableau</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d3ebe703eaedf55</t>
+          <t>https://www.indeed.com/viewjob?jk=3e2322616683445e</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GPU MLOps Engineer</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Molex</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.2</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, Azure ML, MLflow, Docker, Kubernetes, AKS, CI/CD, Terraform, Power BI, R</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Snowflake, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bb4337faf7af1cf</t>
+          <t>https://www.indeed.com/viewjob?jk=b5ae117696ae2b3c</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GPU MLOps Engineer</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Molex</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, Azure ML, MLflow, Docker, Kubernetes, AKS, CI/CD, Terraform, Power BI, R</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Snowflake, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27bc057c56cea960</t>
+          <t>https://www.indeed.com/viewjob?jk=e49708d8edca6e04</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Snowflake_DBT Developers</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.1</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>S3, Glue, Data Lake, CI/CD, Terraform, Snowflake, Python, SQL, R, Scala</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Snowflake, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acb81b67805de775</t>
+          <t>https://www.indeed.com/viewjob?jk=c7bc23cafde3de00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Intern - Data Full Stack Engineer</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Data Lake, CI/CD, Snowflake, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Snowflake, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=861b5b837191e360</t>
+          <t>https://www.indeed.com/viewjob?jk=6a04069d3f3584ed</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Berxi</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Specialty Insurance</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, GitHub Actions, Git, Databricks, NoSQL, Power BI, SQL, R, Scala</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Snowflake, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdcd811be7d4a19d</t>
+          <t>https://www.indeed.com/viewjob?jk=7f02fd8499365382</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Asynchronous Processing</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Klaviyo</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, FastAPI, Kubernetes, Terraform, Git, Kafka, Python, R, Scala</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Snowflake, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bed4367aac850f3</t>
+          <t>https://www.indeed.com/viewjob?jk=3f3984756cdac147</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Analyst III/Sr</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>EQT Corporation</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Canonsburg, PA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Git, Databricks, Power BI, Python, SQL, R, Scala</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Snowflake, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,7 +846,2667 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdf2419224aa656d</t>
+          <t>https://www.indeed.com/viewjob?jk=b605dce7b0600d93</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Senior Full Stack .NET Developer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Team Velocity Marketing</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Cleveland, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Snowflake, Kafka, PostgreSQL, MySQL</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2e82c34131ee2765</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Senior Full Stack .NET Developer</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Team Velocity Marketing</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Snowflake, Kafka, PostgreSQL, MySQL</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=22bf48116516e1d7</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Newmark</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, Copilot, Kinesis, Docker, Kubernetes, CI/CD, Kafka, NoSQL</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cecea5a726201bd5</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>SW Engineer / AI Enterprise Systems Analyst</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Zebra Technologies</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Lincolnshire, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, LLaMA, Gemini, Copilot, Prompt Engineering, CI/CD, Git, NoSQL</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0e010f47923f4e60</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Senior Agentic AI Engineer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>T. Mims Corp.</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Lakeland, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Hugging Face, PyTorch, FastAPI, Docker, Kubernetes, CI/CD, PostgreSQL, Python</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=595818c369f4d234</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Full-Stack</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Recurly</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Broomfield, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, CI/CD, Git, Kafka, MySQL, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b9d84694739986e5</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Intermediate DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Citi</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a673f5c6b08fd054</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer - NBA</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Copilot, Data Lake, Git, Databricks, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a6252cdef37affd1</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Sperry Rail</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Shelton, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, S3, Glue, MLflow, Docker, CI/CD, Git, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7aee3bddf93c206b</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Enterprise Architect</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Infoverity</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Dublin, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Data Lake, Terraform, Git, Snowflake, Databricks, Kafka, Tableau, Power BI, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=05f507aa8170f412</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>AI Engineering Intern</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0403098d9ed8619c</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>doctronic</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, S3, Glue, Kinesis, Snowflake, Databricks, PostgreSQL, MongoDB, Python</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f2a1804955dab550</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Senior Full-Stack Engineer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Primary Design, Inc</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, PostgreSQL, MySQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dcba715e993d2a93</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>AI Infrastructure &amp; Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>International Materials Inc</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Delray Beach, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, Gemini, Hugging Face, Docker, Kubernetes, CI/CD, Terraform, R</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=00ea0a6fd26257d7</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Data Scientist I</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Chewy</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Data Scientist, Glue, Athena, Redshift, Snowflake, Redshift, Tableau, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=94d3b59f9621415c</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Quant Analyst- Senior Associate</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>RAG, Git, Snowflake, Tableau, Python, SQL, R, Scala, Optimization, Hypothesis Testing</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9ed3b236aa8ba85a</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Quant Analytics Senior Associate - Credit Card Installment</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Wilmington, DE, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RAG, Git, Snowflake, Tableau, Python, SQL, R, Scala, Optimization, Hypothesis Testing</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=df120abdc50c8e08</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>AI Technical Consultant</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Copilot, Prompt Engineering, Git, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=875dc8a7f032e65f</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Software Engineer, Core Platform (All Levels)</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RAG, S3, FastAPI, Docker, PostgreSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9db1f65a35af61fc</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Software Engineer, Core Platform (All Levels)</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>RAG, S3, FastAPI, Docker, PostgreSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a641d5c2a17d04f4</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Software Engineer, Core Platform (All Levels)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>RAG, S3, FastAPI, Docker, PostgreSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bc9f6bf581e0a0c7</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Software Engineer, Core Platform (All Levels)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>RAG, S3, FastAPI, Docker, PostgreSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b3bf55236bfd7dd7</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Software Engineer, Core Platform (All Levels)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>RAG, S3, FastAPI, Docker, PostgreSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=afb6c48542d9332a</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Software Engineer, Core Platform (All Levels)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>RAG, S3, FastAPI, Docker, PostgreSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0034aaa53a7049d4</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Sr Cloud Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Happen Bank</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Lehi, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f4e748964b56e3dd</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Sr Cloud Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Happen Bank</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d0101421529dd218</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>AI First Engineer – Oracle SCM Applications Suite</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Bedminster, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Git, SQL, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ea10cadf3dcfa970</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>AI-Enabled Oracle SCM/EBS Engineer</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Git, SQL, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=851ff29b0fce635d</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Senior Project Coordinator</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Git, SQL, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8874c2142a0bc3be</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>AI-First Oracle SCM Engineer - Onsite</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Git, SQL, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3c9dbf69d7722094</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>AI-First Oracle SCM Engineer- Onsite</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Git, SQL, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=11436f40251c2dcc</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Java Software Engineer III</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Git, Kafka, Cassandra, NoSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ab128f11077d98dd</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Prompt Engineering, CI/CD, Git, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=994a767c58faa7a4</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence Co-Op/Intern - Spring 2027</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>The Mosaic Company</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>10</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a3b3a5d5829685f3</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Software Engineer I</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Robert Half</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>San Ramon, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>10</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=800990140a022e31</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>OT Integration Engineer</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>KINETIK</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Midland, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>10</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Snowflake, Databricks, Power BI, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0eac11046aeec660</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Solution Architect – Snowflake &amp; AWS Data Platform</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>10</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Cortex, CI/CD, Snowflake, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e20b98016fd39445</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>10</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fb9706788872b5f1</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Springfield, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>10</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c05dcd401c2ff976</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>South Bend, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>10</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fdb4cc62278bf392</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>10</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ab8c82b027dd2c01</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>10</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a35ef0cf2aa7b657</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>10</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b38289c64eb19de3</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>10</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dae39801e6ebb135</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Oakbrook Terrace, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>10</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8f2d68b0b01c429f</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Cleveland, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>10</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b73ddb1a8be228bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>10</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a44001aa2039e902</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>10</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6f28be653e5deb6a</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>10</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4d20e83a6832e880</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>10</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=914fbf079add4bd5</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Fort Wayne, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>10</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=53864d0647193d42</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>10</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aae6f8b7939f6cb6</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>10</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f29ca92109574e76</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>10</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fc6913831e7cbc00</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Costa Mesa, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>10</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=adfcce8ec91e6fb5</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>10</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=99ccf21ee1949018</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Boca Raton, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>10</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e189917e7e893284</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Louisville, KY, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>10</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2f3503637dcab48e</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>10</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=304431a8edc53053</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Burlington, VT, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>10</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4c0a99fa5059e039</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Lexington, KY, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>10</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=801fe823a6643ee5</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>10</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b7750ac329857d96</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>10</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1e68d56fece499c5</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Sacramento, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>10</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8a3c1c3cdd15f49a</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Knoxville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>10</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6af6acae6ddc5338</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Sarasota, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>10</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d5a8fde59928c7b0</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>10</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cd3558d20c41bfda</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>10</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=57e7d2bc2390eda1</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Livingston, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6fa51b16fd453ceb</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>The Woodlands, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>10</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1432d14332e56d3f</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=93f5a079d74a1327</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Grand Rapids, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>10</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fdb8fc757bd0cb13</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>10</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=541bef373a49b9d8</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Tallahassee, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>10</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=524e4440ba868a5c</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Data &amp; AI Sales Solutions Architect</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>AllCloud</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>10</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Generative AI, Glue, Redshift, Data Lake, Kinesis, Snowflake, Databricks, Redshift, R</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=702d1760d0562748</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Data Architect</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Quality Insights</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>10</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Synapse, Terraform, Snowflake, Databricks, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ff47e82bfc5817a2</t>
         </is>
       </c>
     </row>
